--- a/파이썬/코딩교실 매크로/1.코딩교실준비/5.LMS줌링크/LMS줌링크.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/5.LMS줌링크/LMS줌링크.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\5.LMS줌링크\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E980052-C1BA-4800-830F-6EEDD1F6B400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA63DD5-65CB-4A73-A034-8CB7A068E2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45990" yWindow="2190" windowWidth="28305" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44235" yWindow="2595" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="77">
   <si>
     <t>admin ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -160,60 +160,6 @@
     <t>BG_MW_18</t>
   </si>
   <si>
-    <t>https://us02web.zoom.us/j/83854664632?pwd=QV8BEwYo6P8pha6cCaIvmMLhrN7RXa.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/82439279836?pwd=btQpNqXSwkKuMAzf0oC917vFHSUYFJ.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/82963803147?pwd=38RktIafA4foy38Rtc2CdKvFiuo2Dj.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/83375912206?pwd=K0kSIVjw9SnD7UYMhsKSLa0mJroB6d.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/83657838236?pwd=0VjqAF87qLqlL6loM4C9Ti3Tv26d8J.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/86548325560?pwd=kt26K8MfybniREMdIYBXId1F26j0lM.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/84992364309?pwd=ZUEVvCqatVGD6yy35EcitwhS2eBoLb.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/84390877253?pwd=O2Bi2MYKRLj4eQioH54qprvJwoJYj1.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/86984890925?pwd=ieR4QDBkSbQh9eK94lAmqzqbeacXWL.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/84762814721?pwd=dOKX7lkCHI6i5bjQytvfip1GWhKF2i.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/81189595257?pwd=pD4fY7PjhT3QKh6UEiEUPnXKdMVhdy.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/86048581601?pwd=wmWTot6vaDzYJzxqs4ezBTmxOSPpjZ.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/81314117731?pwd=j6Opwdm2GEbz2c2y3YoIxgSOvGyIIT.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/84278187289?pwd=hM6onMvOdpxn3nI2a5QXOCHx0xslhH.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/86171472596?pwd=YwZ0BDayWfgHLuXrpV6PWmFvit7DaV.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/81340115605?pwd=yDtoKK83qDUwkcPsSuSlsG7FIJTHbk.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/89120474985?pwd=Mso8yXiWq8mmpEzWqUfiehzXKGDg4g.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/82285886710?pwd=BuP3E7DWe9y6Xp33BkCZGfbfqVQbtb.1</t>
-  </si>
-  <si>
     <t>BG_TT_01</t>
   </si>
   <si>
@@ -266,6 +212,78 @@
   </si>
   <si>
     <t>BG_TT_18</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/85704835326?pwd=YxLXn49yzOFblClNpzkeHD1d15pl7Y.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/83563070924?pwd=ACvTUrF9nZFvd3Fr5gIzRPKX3GKMIE.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/84831932165?pwd=dKGqAQDQV7Djg3hPpOaWZCEeCTn38a.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/88962540887?pwd=qKbdpbH5hayzhQiVI5dIIbRjocBBXU.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/86296741626?pwd=TVff4oxRugzuDwuR29pUbyF4XPbAKd.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/83013925394?pwd=YFe8pBLyVZ5cdD2SJlMsTGL2BbLrXT.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/85986652064?pwd=QayJZlKeN9iSAJaF7lif4ReNLawezr.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/89917256921?pwd=Nodhj8VbQITA4IybMHIfVvhfwTiSaF.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/86818278887?pwd=68uPqUSqUZ7YxLIQ8LcUKFQEAdyQzI.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/88508559873?pwd=m3qZxo19Gjc4GvG2n9XNUuAdsWLviJ.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/81694843305?pwd=ygnKvG1LOTDViejkbjDcdGR6djPoyK.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/82820244472?pwd=yBm6VTQaTt56bHrnma1rf4BGSobXbF.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/88550820645?pwd=3xGexw2s1GEkpoboYx9fZ3e91AXPtn.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/89267054774?pwd=pB6yYaiybb1GsxJLjgzgJcBjuBaBgr.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/87481279863?pwd=wAxjnajBbbdykfhrhUYRf78kAbaxYI.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/83729949909?pwd=a4qT8AKGkL9YOgic6y7BYcEw7PRePz.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/84381439746?pwd=lGihpQXIbhqN71GYOPrcRCVeKCy6y7.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/89828821645?pwd=Jbu7yJCuXqXbtJnWZrEq3hPtaCEOu4.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/84946198891?pwd=YS0puaT5SS0sLbuLbaIuPRTC3PVlh9.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/88629906192?pwd=ClfMqFS1dZ4rCI3hze6QNI6VnoVjkc.1</t>
+  </si>
+  <si>
+    <t>BG_MW_19</t>
+  </si>
+  <si>
+    <t>BG_MW_20</t>
+  </si>
+  <si>
+    <t>BG_TT_19</t>
+  </si>
+  <si>
+    <t>BG_TT_20</t>
   </si>
 </sst>
 </file>
@@ -353,7 +371,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -421,6 +439,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -431,7 +464,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -487,6 +520,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -847,7 +883,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C2" s="8"/>
       <c r="F2" s="4"/>
@@ -865,7 +901,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C3" s="6"/>
       <c r="F3" s="4"/>
@@ -883,7 +919,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C4" s="6"/>
       <c r="F4" s="4"/>
@@ -901,7 +937,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C5" s="6"/>
       <c r="F5" s="4"/>
@@ -913,7 +949,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C6" s="6"/>
       <c r="F6" s="4"/>
@@ -925,7 +961,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C7" s="6"/>
       <c r="F7" s="4"/>
@@ -943,7 +979,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C8" s="6"/>
       <c r="F8" s="4"/>
@@ -958,7 +994,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C9" s="7"/>
       <c r="F9" s="4"/>
@@ -976,7 +1012,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C10" s="6"/>
       <c r="F10" s="4"/>
@@ -990,8 +1026,8 @@
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>44</v>
+      <c r="B11" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="C11" s="6"/>
       <c r="F11" s="4"/>
@@ -1009,7 +1045,7 @@
         <v>27</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C12" s="6"/>
       <c r="F12" s="4"/>
@@ -1024,7 +1060,7 @@
         <v>28</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C13" s="6"/>
       <c r="F13" s="4"/>
@@ -1036,7 +1072,7 @@
         <v>29</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C14" s="6"/>
       <c r="F14" s="4"/>
@@ -1048,7 +1084,7 @@
         <v>30</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C15" s="6"/>
       <c r="F15" s="4"/>
@@ -1060,7 +1096,7 @@
         <v>31</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C16" s="6"/>
       <c r="F16" s="4"/>
@@ -1071,8 +1107,8 @@
       <c r="A17" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>50</v>
+      <c r="B17" s="19" t="s">
+        <v>68</v>
       </c>
       <c r="C17" s="8"/>
       <c r="F17" s="4"/>
@@ -1084,7 +1120,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C18" s="6"/>
       <c r="F18" s="4"/>
@@ -1096,7 +1132,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C19" s="6"/>
       <c r="F19" s="4"/>
@@ -1104,11 +1140,11 @@
       <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A20" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>35</v>
+      <c r="A20" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="C20" s="6"/>
       <c r="F20" s="4"/>
@@ -1117,10 +1153,10 @@
     </row>
     <row r="21" spans="1:11" ht="17.25" thickBot="1">
       <c r="A21" s="11" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="C21" s="6"/>
       <c r="F21" s="4"/>
@@ -1128,11 +1164,11 @@
       <c r="K21" s="4"/>
     </row>
     <row r="22" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A22" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>37</v>
+      <c r="A22" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>53</v>
       </c>
       <c r="C22" s="6"/>
       <c r="F22" s="4"/>
@@ -1141,10 +1177,10 @@
     </row>
     <row r="23" spans="1:11" ht="17.25" thickBot="1">
       <c r="A23" s="11" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C23" s="13"/>
       <c r="F23" s="4"/>
@@ -1153,10 +1189,10 @@
     </row>
     <row r="24" spans="1:11" ht="17.25" thickBot="1">
       <c r="A24" s="12" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C24" s="7"/>
       <c r="F24" s="4"/>
@@ -1165,10 +1201,10 @@
     </row>
     <row r="25" spans="1:11" ht="17.25" thickBot="1">
       <c r="A25" s="11" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C25" s="6"/>
       <c r="F25" s="4"/>
@@ -1177,10 +1213,10 @@
     </row>
     <row r="26" spans="1:11" ht="17.25" thickBot="1">
       <c r="A26" s="12" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C26" s="6"/>
       <c r="F26" s="4"/>
@@ -1189,10 +1225,10 @@
     </row>
     <row r="27" spans="1:11" ht="17.25" thickBot="1">
       <c r="A27" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C27" s="6"/>
       <c r="F27" s="4"/>
@@ -1201,10 +1237,10 @@
     </row>
     <row r="28" spans="1:11" ht="17.25" thickBot="1">
       <c r="A28" s="12" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C28" s="6"/>
       <c r="F28" s="4"/>
@@ -1213,10 +1249,10 @@
     </row>
     <row r="29" spans="1:11" ht="18" thickTop="1" thickBot="1">
       <c r="A29" s="11" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C29" s="8"/>
       <c r="F29" s="4"/>
@@ -1225,10 +1261,10 @@
     </row>
     <row r="30" spans="1:11" ht="17.25" thickBot="1">
       <c r="A30" s="12" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="C30" s="6"/>
       <c r="F30" s="4"/>
@@ -1237,10 +1273,10 @@
     </row>
     <row r="31" spans="1:11" ht="17.25" thickBot="1">
       <c r="A31" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>46</v>
+        <v>44</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="C31" s="6"/>
       <c r="F31" s="4"/>
@@ -1249,10 +1285,10 @@
     </row>
     <row r="32" spans="1:11" ht="17.25" thickBot="1">
       <c r="A32" s="12" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C32" s="6"/>
       <c r="F32" s="4"/>
@@ -1261,10 +1297,10 @@
     </row>
     <row r="33" spans="1:11" ht="17.25" thickBot="1">
       <c r="A33" s="11" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="C33" s="6"/>
       <c r="F33" s="4"/>
@@ -1273,10 +1309,10 @@
     </row>
     <row r="34" spans="1:11" ht="17.25" thickBot="1">
       <c r="A34" s="12" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C34" s="6"/>
       <c r="F34" s="4"/>
@@ -1285,10 +1321,10 @@
     </row>
     <row r="35" spans="1:11" ht="17.25" thickBot="1">
       <c r="A35" s="11" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C35" s="6"/>
       <c r="F35" s="4"/>
@@ -1297,10 +1333,10 @@
     </row>
     <row r="36" spans="1:11" ht="17.25" thickBot="1">
       <c r="A36" s="12" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C36" s="7"/>
       <c r="F36" s="4"/>
@@ -1309,10 +1345,10 @@
     </row>
     <row r="37" spans="1:11" ht="17.25" thickBot="1">
       <c r="A37" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>68</v>
       </c>
       <c r="C37" s="6"/>
       <c r="F37" s="4"/>
@@ -1320,32 +1356,48 @@
       <c r="K37" s="4"/>
     </row>
     <row r="38" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A38" s="4"/>
-      <c r="B38" s="9"/>
+      <c r="A38" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>69</v>
+      </c>
       <c r="C38" s="6"/>
       <c r="F38" s="4"/>
       <c r="G38" s="2"/>
       <c r="K38" s="4"/>
     </row>
     <row r="39" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A39" s="4"/>
-      <c r="B39" s="9"/>
+      <c r="A39" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="C39" s="6"/>
       <c r="F39" s="4"/>
       <c r="G39" s="2"/>
       <c r="K39" s="4"/>
     </row>
     <row r="40" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A40" s="4"/>
-      <c r="B40" s="9"/>
+      <c r="A40" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>71</v>
+      </c>
       <c r="C40" s="6"/>
       <c r="F40" s="4"/>
       <c r="G40" s="2"/>
       <c r="K40" s="4"/>
     </row>
     <row r="41" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A41" s="4"/>
-      <c r="B41" s="9"/>
+      <c r="A41" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>72</v>
+      </c>
       <c r="C41" s="6"/>
       <c r="F41" s="4"/>
       <c r="G41" s="2"/>
@@ -1420,52 +1472,56 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B19" r:id="rId1" xr:uid="{1A1EF154-7615-4B9B-8BF1-E019278FB8F1}"/>
-    <hyperlink ref="B18" r:id="rId2" xr:uid="{62544557-1665-49C0-B7EA-4C4B902683C0}"/>
-    <hyperlink ref="B17" r:id="rId3" xr:uid="{C3AC6FDA-4F75-47EE-97E0-6A876700C541}"/>
-    <hyperlink ref="B16" r:id="rId4" xr:uid="{65090046-46EC-4DCD-A9B6-FD12C70F7DB2}"/>
-    <hyperlink ref="B15" r:id="rId5" xr:uid="{FB4C4052-4050-4B61-90BC-50B3E9FA2749}"/>
-    <hyperlink ref="B14" r:id="rId6" xr:uid="{D41255C0-8D37-481B-9D38-3D7FD5C43FA1}"/>
-    <hyperlink ref="B13" r:id="rId7" xr:uid="{880E55CE-B42B-4618-B226-4B022417F8D2}"/>
-    <hyperlink ref="B12" r:id="rId8" xr:uid="{AFF8DFF2-3F0B-44E6-A1BC-0BD3AB9BED0F}"/>
-    <hyperlink ref="B11" r:id="rId9" xr:uid="{CADA6FD9-8FED-4C6F-9D8D-B02DF8D17C21}"/>
-    <hyperlink ref="B10" r:id="rId10" xr:uid="{225D2A44-FEAB-4939-9221-4CBB4F11C5B0}"/>
-    <hyperlink ref="B9" r:id="rId11" xr:uid="{C5B5998A-A5B3-4240-B872-450E689396E8}"/>
-    <hyperlink ref="B8" r:id="rId12" xr:uid="{70B13C22-DBFA-438D-AAD1-85318E2C5E2A}"/>
-    <hyperlink ref="B7" r:id="rId13" xr:uid="{F5B8F013-9026-444D-91D6-10F7995147FD}"/>
-    <hyperlink ref="B6" r:id="rId14" xr:uid="{39DFA172-A294-442E-8F79-7F3BA90991F2}"/>
-    <hyperlink ref="B5" r:id="rId15" xr:uid="{D217F8E2-2E70-4351-87F7-F06220B6F136}"/>
-    <hyperlink ref="B4" r:id="rId16" xr:uid="{8983A0F9-278C-41D2-9219-E63FD74F2638}"/>
-    <hyperlink ref="B3" r:id="rId17" xr:uid="{7CC9E3FA-E621-4D5D-B83F-1F1D87BA719D}"/>
-    <hyperlink ref="B2" r:id="rId18" xr:uid="{EA7E7F47-D62B-4B8B-9551-5BB0188E7B95}"/>
-    <hyperlink ref="Q1" r:id="rId19" xr:uid="{FE21F267-E533-4861-88D0-C07536AB6D58}"/>
-    <hyperlink ref="Q2" r:id="rId20" xr:uid="{9FFE7ACE-1824-4C57-9BE1-CD3455AEF567}"/>
-    <hyperlink ref="Q7" r:id="rId21" xr:uid="{2F15D1DC-4C2D-4B8F-9E46-EA9A5702A39B}"/>
-    <hyperlink ref="Q9" r:id="rId22" xr:uid="{B810DE77-7A3B-465F-B768-9300AA75E360}"/>
-    <hyperlink ref="Q10" r:id="rId23" xr:uid="{045248DF-4C4F-47FD-80F3-BD1D5FEF4441}"/>
-    <hyperlink ref="Q8" r:id="rId24" xr:uid="{3477DE43-A923-49D1-9667-8086CCC36BC6}"/>
-    <hyperlink ref="Q12" r:id="rId25" xr:uid="{89C02FA0-7825-47D3-A436-BFC9A9FA2DBA}"/>
-    <hyperlink ref="Q11" r:id="rId26" xr:uid="{F2A7AEFA-0A9D-4E62-9B56-23C5471E41EA}"/>
-    <hyperlink ref="B20" r:id="rId27" xr:uid="{AAB31586-67FF-4A1A-8B24-6971B0875FF0}"/>
-    <hyperlink ref="B21" r:id="rId28" xr:uid="{245C8C72-9CD2-42F9-B15E-8FF37BDA01B6}"/>
-    <hyperlink ref="B22" r:id="rId29" xr:uid="{F9B54AAB-E4E2-4C14-9292-E77F1E0EA95A}"/>
-    <hyperlink ref="B23" r:id="rId30" xr:uid="{966FE1FF-D0EA-4D50-AE38-98476C99AF79}"/>
-    <hyperlink ref="B24" r:id="rId31" xr:uid="{094FA704-F4B6-4272-A4C3-FC5D7A81BBA1}"/>
-    <hyperlink ref="B25" r:id="rId32" xr:uid="{0606FED5-6680-4DA8-A04B-9FFB4A6E7009}"/>
-    <hyperlink ref="B26" r:id="rId33" xr:uid="{5B19F209-DE22-4AA7-8E58-EE272122F7A7}"/>
-    <hyperlink ref="B27" r:id="rId34" xr:uid="{1C07A0B9-B94E-49E5-93C7-D77B2B725E16}"/>
-    <hyperlink ref="B28" r:id="rId35" xr:uid="{607CAB4B-F3B1-466F-A990-7DF84473FD21}"/>
-    <hyperlink ref="B29" r:id="rId36" xr:uid="{750A67E2-B8C6-4C98-9FC3-44071FBBCFEA}"/>
-    <hyperlink ref="B30" r:id="rId37" xr:uid="{4B1D28EF-75EE-4A3A-B86F-C14AE4C13CE7}"/>
-    <hyperlink ref="B31" r:id="rId38" xr:uid="{2940A6DC-6D05-4A97-A0CA-1A59BFC57DF7}"/>
-    <hyperlink ref="B32" r:id="rId39" xr:uid="{EA52C76E-F8EE-437B-A764-12ED37E86D88}"/>
-    <hyperlink ref="B33" r:id="rId40" xr:uid="{7DF584ED-8439-440F-8200-65FDD97DC912}"/>
-    <hyperlink ref="B34" r:id="rId41" xr:uid="{B388AFA1-7E75-4C52-8736-66E2370FFD4D}"/>
-    <hyperlink ref="B35" r:id="rId42" xr:uid="{2A930D2F-0C5D-49AA-96EB-114EFC8F1308}"/>
-    <hyperlink ref="B36" r:id="rId43" xr:uid="{B63C8F7B-094B-4DD5-B168-338A32CCF4D2}"/>
-    <hyperlink ref="B37" r:id="rId44" xr:uid="{291D221B-5D9E-4A02-933C-BBD8C9E7B480}"/>
+    <hyperlink ref="Q1" r:id="rId1" xr:uid="{FE21F267-E533-4861-88D0-C07536AB6D58}"/>
+    <hyperlink ref="Q2" r:id="rId2" xr:uid="{9FFE7ACE-1824-4C57-9BE1-CD3455AEF567}"/>
+    <hyperlink ref="Q7" r:id="rId3" xr:uid="{2F15D1DC-4C2D-4B8F-9E46-EA9A5702A39B}"/>
+    <hyperlink ref="Q9" r:id="rId4" xr:uid="{B810DE77-7A3B-465F-B768-9300AA75E360}"/>
+    <hyperlink ref="Q10" r:id="rId5" xr:uid="{045248DF-4C4F-47FD-80F3-BD1D5FEF4441}"/>
+    <hyperlink ref="Q8" r:id="rId6" xr:uid="{3477DE43-A923-49D1-9667-8086CCC36BC6}"/>
+    <hyperlink ref="Q12" r:id="rId7" xr:uid="{89C02FA0-7825-47D3-A436-BFC9A9FA2DBA}"/>
+    <hyperlink ref="Q11" r:id="rId8" xr:uid="{F2A7AEFA-0A9D-4E62-9B56-23C5471E41EA}"/>
+    <hyperlink ref="B2" r:id="rId9" xr:uid="{0AFC7F36-0558-49B1-B2F6-D91869F51030}"/>
+    <hyperlink ref="B3" r:id="rId10" xr:uid="{BBAB0743-54BE-423B-8C16-E18E6E1E4841}"/>
+    <hyperlink ref="B4" r:id="rId11" xr:uid="{8127CDC9-87CE-4C66-A8AF-8D45D61DAF4D}"/>
+    <hyperlink ref="B5" r:id="rId12" xr:uid="{852E5A38-45EB-4AD5-AE2D-22EF9086227F}"/>
+    <hyperlink ref="B6" r:id="rId13" xr:uid="{2A768213-2ED0-4D0B-A1B0-C1CAD783C141}"/>
+    <hyperlink ref="B7" r:id="rId14" xr:uid="{0DB1151B-B09D-4A38-91F2-EF044CC8FBCE}"/>
+    <hyperlink ref="B8" r:id="rId15" xr:uid="{9249A50C-40C8-4444-A0CE-9768526FA93D}"/>
+    <hyperlink ref="B9" r:id="rId16" xr:uid="{BEFAE6E9-8465-4E3C-87DA-75CA137290D2}"/>
+    <hyperlink ref="B10" r:id="rId17" xr:uid="{4D20A9AF-FD93-4072-B4A3-927FECB3A832}"/>
+    <hyperlink ref="B11" r:id="rId18" xr:uid="{3D2BEB49-EEE4-4196-861E-A9E5458BB091}"/>
+    <hyperlink ref="B12" r:id="rId19" xr:uid="{8E2B3C57-F7A9-4434-932B-0546FE34E890}"/>
+    <hyperlink ref="B13" r:id="rId20" xr:uid="{942F9D2D-CD35-4768-A578-C67E235FA74A}"/>
+    <hyperlink ref="B14" r:id="rId21" xr:uid="{4C836726-B4A2-49EC-810A-210030A4C2E3}"/>
+    <hyperlink ref="B15" r:id="rId22" xr:uid="{64561732-E3F8-4D9B-B4BC-BE202314B021}"/>
+    <hyperlink ref="B16" r:id="rId23" xr:uid="{2E2B4E1F-F20C-4771-A9FA-D770BC6C792A}"/>
+    <hyperlink ref="B17" r:id="rId24" xr:uid="{B4E6E8CC-C8EB-4ECC-8E15-E0F948C9BBA3}"/>
+    <hyperlink ref="B18" r:id="rId25" xr:uid="{30A55AF1-BFAB-4226-8452-6EC02665D7A7}"/>
+    <hyperlink ref="B19" r:id="rId26" xr:uid="{F17F0B7A-355C-42BE-A8A8-57229D500DFC}"/>
+    <hyperlink ref="B20" r:id="rId27" xr:uid="{02BAFC1F-A5EC-4C88-834D-EA254E8E7932}"/>
+    <hyperlink ref="B21" r:id="rId28" xr:uid="{46F1DACC-8279-4B65-B2E8-180FFD6A6099}"/>
+    <hyperlink ref="B22" r:id="rId29" xr:uid="{5A58FFEC-4163-4E9A-B9F0-63D7831237B9}"/>
+    <hyperlink ref="B23" r:id="rId30" xr:uid="{95537EFC-16D6-470E-A2A4-7223F8B77776}"/>
+    <hyperlink ref="B24" r:id="rId31" xr:uid="{4AFC6CD5-0CAE-4A18-A91F-072629FEE2A7}"/>
+    <hyperlink ref="B25" r:id="rId32" xr:uid="{1239B683-53FA-4E6C-8748-64E9DD71A754}"/>
+    <hyperlink ref="B26" r:id="rId33" xr:uid="{2F6E1D28-79CC-48FD-9520-188E0D4B9E6E}"/>
+    <hyperlink ref="B27" r:id="rId34" xr:uid="{1FE1900E-6AF8-4F52-BA70-B284B18ABBF1}"/>
+    <hyperlink ref="B28" r:id="rId35" xr:uid="{920FFFE5-9468-4AD7-953E-D6E1FD236CD0}"/>
+    <hyperlink ref="B29" r:id="rId36" xr:uid="{B87DAAA4-9E6E-44C4-9AFE-31018ED64428}"/>
+    <hyperlink ref="B30" r:id="rId37" xr:uid="{C9832A31-EDDE-4889-924D-436B55352EE6}"/>
+    <hyperlink ref="B31" r:id="rId38" xr:uid="{75C8795A-C2A3-492B-90D3-BF56A55E4997}"/>
+    <hyperlink ref="B32" r:id="rId39" xr:uid="{FC1696D1-EA78-4B1E-AC1F-60A18B78688C}"/>
+    <hyperlink ref="B33" r:id="rId40" xr:uid="{AB2E2D32-FFB1-4173-A121-E55F2D1CA349}"/>
+    <hyperlink ref="B34" r:id="rId41" xr:uid="{EA0DC3A3-AD62-48D3-BF2A-18FC1DA6A76A}"/>
+    <hyperlink ref="B35" r:id="rId42" xr:uid="{F801BE89-3ECD-48AE-9DB8-1C7E370ED74D}"/>
+    <hyperlink ref="B36" r:id="rId43" xr:uid="{CC30559D-78B7-4913-A852-BDE30DD40E2A}"/>
+    <hyperlink ref="B37" r:id="rId44" xr:uid="{90BED1DC-6EAC-4612-AF41-D394975532C8}"/>
+    <hyperlink ref="B38" r:id="rId45" xr:uid="{EADA49FE-8D29-4BA3-9877-FBBC51AED99F}"/>
+    <hyperlink ref="B39" r:id="rId46" xr:uid="{A06BC502-A2F2-4E26-BB67-1A1A6E9ED3E8}"/>
+    <hyperlink ref="B40" r:id="rId47" xr:uid="{46FB51B6-8731-4537-BE86-D0B3F6C1845F}"/>
+    <hyperlink ref="B41" r:id="rId48" xr:uid="{BEC72745-9257-4390-9D76-0A909665AE11}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId45"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId49"/>
 </worksheet>
 </file>
--- a/파이썬/코딩교실 매크로/1.코딩교실준비/5.LMS줌링크/LMS줌링크.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/5.LMS줌링크/LMS줌링크.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\5.LMS줌링크\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA63DD5-65CB-4A73-A034-8CB7A068E2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C466CBB-74E3-497D-B1FF-28E8DDAB6079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44235" yWindow="2595" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34455" yWindow="2505" windowWidth="28860" windowHeight="17370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="73">
   <si>
     <t>admin ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -214,57 +214,12 @@
     <t>BG_TT_18</t>
   </si>
   <si>
-    <t>https://us02web.zoom.us/j/85704835326?pwd=YxLXn49yzOFblClNpzkeHD1d15pl7Y.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/83563070924?pwd=ACvTUrF9nZFvd3Fr5gIzRPKX3GKMIE.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/84831932165?pwd=dKGqAQDQV7Djg3hPpOaWZCEeCTn38a.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/88962540887?pwd=qKbdpbH5hayzhQiVI5dIIbRjocBBXU.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/86296741626?pwd=TVff4oxRugzuDwuR29pUbyF4XPbAKd.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/83013925394?pwd=YFe8pBLyVZ5cdD2SJlMsTGL2BbLrXT.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/85986652064?pwd=QayJZlKeN9iSAJaF7lif4ReNLawezr.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/89917256921?pwd=Nodhj8VbQITA4IybMHIfVvhfwTiSaF.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/86818278887?pwd=68uPqUSqUZ7YxLIQ8LcUKFQEAdyQzI.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/88508559873?pwd=m3qZxo19Gjc4GvG2n9XNUuAdsWLviJ.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/81694843305?pwd=ygnKvG1LOTDViejkbjDcdGR6djPoyK.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/82820244472?pwd=yBm6VTQaTt56bHrnma1rf4BGSobXbF.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/88550820645?pwd=3xGexw2s1GEkpoboYx9fZ3e91AXPtn.1</t>
-  </si>
-  <si>
     <t>https://us02web.zoom.us/j/89267054774?pwd=pB6yYaiybb1GsxJLjgzgJcBjuBaBgr.1</t>
   </si>
   <si>
     <t>https://us02web.zoom.us/j/87481279863?pwd=wAxjnajBbbdykfhrhUYRf78kAbaxYI.1</t>
   </si>
   <si>
-    <t>https://us02web.zoom.us/j/83729949909?pwd=a4qT8AKGkL9YOgic6y7BYcEw7PRePz.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/84381439746?pwd=lGihpQXIbhqN71GYOPrcRCVeKCy6y7.1</t>
-  </si>
-  <si>
     <t>https://us02web.zoom.us/j/89828821645?pwd=Jbu7yJCuXqXbtJnWZrEq3hPtaCEOu4.1</t>
   </si>
   <si>
@@ -274,23 +229,56 @@
     <t>https://us02web.zoom.us/j/88629906192?pwd=ClfMqFS1dZ4rCI3hze6QNI6VnoVjkc.1</t>
   </si>
   <si>
-    <t>BG_MW_19</t>
-  </si>
-  <si>
-    <t>BG_MW_20</t>
-  </si>
-  <si>
     <t>BG_TT_19</t>
   </si>
   <si>
-    <t>BG_TT_20</t>
+    <t>https://us02web.zoom.us/j/88260643671?pwd=etPerEnQW3KEUlcE2Q7YQQpk3WMmTA.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/81193221983?pwd=dlaX4n2zJJbrzv88yv0Q9w7ezeIlxv.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/85718103327?pwd=NmEhhhRk2aEnQHtwNzYNFglQaET8uQ.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/86217792106?pwd=Knxr51BVj1c7s3bHUhYo2V4vSnKOfI.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/89271860506?pwd=LOyyEtbCJjxFmGd5baRGb3DuY9kIy4.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/81959809961?pwd=QyUjNfW0n3bjrFaw6U3BBua0b07Gxr.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/83983224518?pwd=0H5HHnogqWjHQyaZhrTQWwprObX8Z9.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/84969155425?pwd=X0vlZ5TJOQSwVyVb6GMSHy0xQAiKkv.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/84386193333?pwd=bO3IYLi0jtoUIYLkIduxNtFnn6v0Jt.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/86959584428?pwd=kMvA0at3ciRC3UEF8tOSbQEGwhiwo2.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/86336628154?pwd=KVC2uLz1S7OfLqYXJXJpX3CUwmcLhJ.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/85808556380?pwd=WeJ25UbtJxbDi6WTSQhVBKfcBbSp2E.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/82150657982?pwd=y5poP1hNSQaChg52ee57x1ITzPP4ux.1</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/82381821972?pwd=1wo9aFRAfODSTxoQmQr67VCIinxf8P.1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,8 +338,15 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -370,8 +365,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F3F3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -439,21 +440,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -464,7 +450,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -516,13 +502,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -841,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.625" style="2" bestFit="1" customWidth="1"/>
@@ -882,8 +871,8 @@
       <c r="A2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>53</v>
+      <c r="B2" s="17" t="s">
+        <v>59</v>
       </c>
       <c r="C2" s="8"/>
       <c r="F2" s="4"/>
@@ -900,8 +889,8 @@
       <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>54</v>
+      <c r="B3" s="18" t="s">
+        <v>60</v>
       </c>
       <c r="C3" s="6"/>
       <c r="F3" s="4"/>
@@ -918,8 +907,8 @@
       <c r="A4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>55</v>
+      <c r="B4" s="19" t="s">
+        <v>61</v>
       </c>
       <c r="C4" s="6"/>
       <c r="F4" s="4"/>
@@ -936,8 +925,8 @@
       <c r="A5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>56</v>
+      <c r="B5" s="18" t="s">
+        <v>62</v>
       </c>
       <c r="C5" s="6"/>
       <c r="F5" s="4"/>
@@ -948,8 +937,8 @@
       <c r="A6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>57</v>
+      <c r="B6" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="C6" s="6"/>
       <c r="F6" s="4"/>
@@ -960,8 +949,8 @@
       <c r="A7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>58</v>
+      <c r="B7" s="18" t="s">
+        <v>54</v>
       </c>
       <c r="C7" s="6"/>
       <c r="F7" s="4"/>
@@ -978,8 +967,8 @@
       <c r="A8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>59</v>
+      <c r="B8" s="19" t="s">
+        <v>64</v>
       </c>
       <c r="C8" s="6"/>
       <c r="F8" s="4"/>
@@ -993,8 +982,8 @@
       <c r="A9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>60</v>
+      <c r="B9" s="18" t="s">
+        <v>65</v>
       </c>
       <c r="C9" s="7"/>
       <c r="F9" s="4"/>
@@ -1011,8 +1000,8 @@
       <c r="A10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>61</v>
+      <c r="B10" s="19" t="s">
+        <v>66</v>
       </c>
       <c r="C10" s="6"/>
       <c r="F10" s="4"/>
@@ -1026,8 +1015,8 @@
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>62</v>
+      <c r="B11" s="18" t="s">
+        <v>67</v>
       </c>
       <c r="C11" s="6"/>
       <c r="F11" s="4"/>
@@ -1044,8 +1033,8 @@
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>63</v>
+      <c r="B12" s="19" t="s">
+        <v>68</v>
       </c>
       <c r="C12" s="6"/>
       <c r="F12" s="4"/>
@@ -1059,8 +1048,8 @@
       <c r="A13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>64</v>
+      <c r="B13" s="18" t="s">
+        <v>69</v>
       </c>
       <c r="C13" s="6"/>
       <c r="F13" s="4"/>
@@ -1071,8 +1060,8 @@
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>65</v>
+      <c r="B14" s="19" t="s">
+        <v>53</v>
       </c>
       <c r="C14" s="6"/>
       <c r="F14" s="4"/>
@@ -1083,8 +1072,8 @@
       <c r="A15" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>66</v>
+      <c r="B15" s="18" t="s">
+        <v>70</v>
       </c>
       <c r="C15" s="6"/>
       <c r="F15" s="4"/>
@@ -1095,8 +1084,8 @@
       <c r="A16" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>67</v>
+      <c r="B16" s="19" t="s">
+        <v>55</v>
       </c>
       <c r="C16" s="6"/>
       <c r="F16" s="4"/>
@@ -1107,8 +1096,8 @@
       <c r="A17" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>68</v>
+      <c r="B17" s="18" t="s">
+        <v>56</v>
       </c>
       <c r="C17" s="8"/>
       <c r="F17" s="4"/>
@@ -1119,8 +1108,8 @@
       <c r="A18" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="17" t="s">
-        <v>69</v>
+      <c r="B18" s="19" t="s">
+        <v>57</v>
       </c>
       <c r="C18" s="6"/>
       <c r="F18" s="4"/>
@@ -1131,8 +1120,8 @@
       <c r="A19" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>70</v>
+      <c r="B19" s="20" t="s">
+        <v>71</v>
       </c>
       <c r="C19" s="6"/>
       <c r="F19" s="4"/>
@@ -1140,11 +1129,11 @@
       <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A20" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>71</v>
+      <c r="A20" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>59</v>
       </c>
       <c r="C20" s="6"/>
       <c r="F20" s="4"/>
@@ -1153,10 +1142,10 @@
     </row>
     <row r="21" spans="1:11" ht="17.25" thickBot="1">
       <c r="A21" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>72</v>
+        <v>36</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>60</v>
       </c>
       <c r="C21" s="6"/>
       <c r="F21" s="4"/>
@@ -1164,47 +1153,47 @@
       <c r="K21" s="4"/>
     </row>
     <row r="22" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A22" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="6"/>
+      <c r="A22" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="13"/>
       <c r="F22" s="4"/>
       <c r="G22" s="2"/>
       <c r="K22" s="4"/>
     </row>
     <row r="23" spans="1:11" ht="17.25" thickBot="1">
       <c r="A23" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="13"/>
+        <v>38</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="7"/>
       <c r="F23" s="4"/>
       <c r="G23" s="2"/>
       <c r="K23" s="4"/>
     </row>
     <row r="24" spans="1:11" ht="17.25" thickBot="1">
       <c r="A24" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="7"/>
+        <v>39</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="6"/>
       <c r="F24" s="4"/>
       <c r="G24" s="2"/>
       <c r="K24" s="4"/>
     </row>
     <row r="25" spans="1:11" ht="17.25" thickBot="1">
       <c r="A25" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>56</v>
+        <v>40</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>54</v>
       </c>
       <c r="C25" s="6"/>
       <c r="F25" s="4"/>
@@ -1213,10 +1202,10 @@
     </row>
     <row r="26" spans="1:11" ht="17.25" thickBot="1">
       <c r="A26" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>57</v>
+        <v>41</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>64</v>
       </c>
       <c r="C26" s="6"/>
       <c r="F26" s="4"/>
@@ -1225,46 +1214,46 @@
     </row>
     <row r="27" spans="1:11" ht="17.25" thickBot="1">
       <c r="A27" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>58</v>
+        <v>42</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>65</v>
       </c>
       <c r="C27" s="6"/>
       <c r="F27" s="4"/>
       <c r="G27" s="2"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:11" ht="17.25" thickBot="1">
+    <row r="28" spans="1:11" ht="18" thickTop="1" thickBot="1">
       <c r="A28" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="6"/>
+        <v>43</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="8"/>
       <c r="F28" s="4"/>
       <c r="G28" s="2"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:11" ht="18" thickTop="1" thickBot="1">
+    <row r="29" spans="1:11" ht="17.25" thickBot="1">
       <c r="A29" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="8"/>
+        <v>44</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="6"/>
       <c r="F29" s="4"/>
       <c r="G29" s="2"/>
       <c r="K29" s="4"/>
     </row>
     <row r="30" spans="1:11" ht="17.25" thickBot="1">
       <c r="A30" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>61</v>
+        <v>45</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>68</v>
       </c>
       <c r="C30" s="6"/>
       <c r="F30" s="4"/>
@@ -1273,10 +1262,10 @@
     </row>
     <row r="31" spans="1:11" ht="17.25" thickBot="1">
       <c r="A31" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>62</v>
+        <v>46</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>69</v>
       </c>
       <c r="C31" s="6"/>
       <c r="F31" s="4"/>
@@ -1285,10 +1274,10 @@
     </row>
     <row r="32" spans="1:11" ht="17.25" thickBot="1">
       <c r="A32" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>63</v>
+        <v>47</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>53</v>
       </c>
       <c r="C32" s="6"/>
       <c r="F32" s="4"/>
@@ -1297,10 +1286,10 @@
     </row>
     <row r="33" spans="1:11" ht="17.25" thickBot="1">
       <c r="A33" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>64</v>
+        <v>48</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>70</v>
       </c>
       <c r="C33" s="6"/>
       <c r="F33" s="4"/>
@@ -1309,10 +1298,10 @@
     </row>
     <row r="34" spans="1:11" ht="17.25" thickBot="1">
       <c r="A34" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>65</v>
+        <v>49</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>55</v>
       </c>
       <c r="C34" s="6"/>
       <c r="F34" s="4"/>
@@ -1321,34 +1310,34 @@
     </row>
     <row r="35" spans="1:11" ht="17.25" thickBot="1">
       <c r="A35" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" s="6"/>
+        <v>50</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="7"/>
       <c r="F35" s="4"/>
       <c r="G35" s="2"/>
       <c r="K35" s="4"/>
     </row>
     <row r="36" spans="1:11" ht="17.25" thickBot="1">
       <c r="A36" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" s="7"/>
+        <v>51</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="6"/>
       <c r="F36" s="4"/>
       <c r="G36" s="2"/>
       <c r="K36" s="4"/>
     </row>
     <row r="37" spans="1:11" ht="17.25" thickBot="1">
       <c r="A37" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>68</v>
+        <v>52</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>71</v>
       </c>
       <c r="C37" s="6"/>
       <c r="F37" s="4"/>
@@ -1357,10 +1346,10 @@
     </row>
     <row r="38" spans="1:11" ht="17.25" thickBot="1">
       <c r="A38" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>69</v>
+        <v>58</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="C38" s="6"/>
       <c r="F38" s="4"/>
@@ -1368,53 +1357,41 @@
       <c r="K38" s="4"/>
     </row>
     <row r="39" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A39" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="16" t="s">
-        <v>70</v>
-      </c>
+      <c r="A39" s="12"/>
+      <c r="B39" s="16"/>
       <c r="C39" s="6"/>
       <c r="F39" s="4"/>
       <c r="G39" s="2"/>
       <c r="K39" s="4"/>
     </row>
     <row r="40" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A40" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>71</v>
-      </c>
+      <c r="A40" s="11"/>
+      <c r="B40" s="16"/>
       <c r="C40" s="6"/>
       <c r="F40" s="4"/>
       <c r="G40" s="2"/>
       <c r="K40" s="4"/>
     </row>
     <row r="41" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A41" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>72</v>
-      </c>
+      <c r="A41" s="4"/>
+      <c r="B41" s="9"/>
       <c r="C41" s="6"/>
       <c r="F41" s="4"/>
       <c r="G41" s="2"/>
       <c r="K41" s="4"/>
     </row>
-    <row r="42" spans="1:11" ht="17.25" thickBot="1">
+    <row r="42" spans="1:11" ht="18" thickTop="1" thickBot="1">
       <c r="A42" s="4"/>
       <c r="B42" s="9"/>
-      <c r="C42" s="6"/>
+      <c r="C42" s="8"/>
       <c r="F42" s="4"/>
       <c r="G42" s="2"/>
       <c r="K42" s="4"/>
     </row>
-    <row r="43" spans="1:11" ht="18" thickTop="1" thickBot="1">
+    <row r="43" spans="1:11" ht="17.25" thickBot="1">
       <c r="A43" s="4"/>
       <c r="B43" s="9"/>
-      <c r="C43" s="8"/>
+      <c r="C43" s="6"/>
       <c r="F43" s="4"/>
       <c r="G43" s="2"/>
       <c r="K43" s="4"/>
@@ -1444,30 +1421,22 @@
       <c r="K46" s="4"/>
     </row>
     <row r="47" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A47" s="4"/>
-      <c r="B47" s="9"/>
       <c r="C47" s="6"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="2"/>
-      <c r="K47" s="4"/>
     </row>
     <row r="48" spans="1:11" ht="17.25" thickBot="1">
       <c r="C48" s="6"/>
     </row>
     <row r="49" spans="3:3" ht="17.25" thickBot="1">
-      <c r="C49" s="6"/>
-    </row>
-    <row r="50" spans="3:3" ht="17.25" thickBot="1">
-      <c r="C50" s="7"/>
-    </row>
-    <row r="51" spans="3:3" ht="18" thickTop="1" thickBot="1">
+      <c r="C49" s="7"/>
+    </row>
+    <row r="50" spans="3:3" ht="18" thickTop="1" thickBot="1">
+      <c r="C50" s="6"/>
+    </row>
+    <row r="51" spans="3:3" ht="17.25" thickBot="1">
       <c r="C51" s="6"/>
     </row>
     <row r="52" spans="3:3" ht="17.25" thickBot="1">
       <c r="C52" s="6"/>
-    </row>
-    <row r="53" spans="3:3" ht="17.25" thickBot="1">
-      <c r="C53" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1480,48 +1449,10 @@
     <hyperlink ref="Q8" r:id="rId6" xr:uid="{3477DE43-A923-49D1-9667-8086CCC36BC6}"/>
     <hyperlink ref="Q12" r:id="rId7" xr:uid="{89C02FA0-7825-47D3-A436-BFC9A9FA2DBA}"/>
     <hyperlink ref="Q11" r:id="rId8" xr:uid="{F2A7AEFA-0A9D-4E62-9B56-23C5471E41EA}"/>
-    <hyperlink ref="B2" r:id="rId9" xr:uid="{0AFC7F36-0558-49B1-B2F6-D91869F51030}"/>
-    <hyperlink ref="B3" r:id="rId10" xr:uid="{BBAB0743-54BE-423B-8C16-E18E6E1E4841}"/>
-    <hyperlink ref="B4" r:id="rId11" xr:uid="{8127CDC9-87CE-4C66-A8AF-8D45D61DAF4D}"/>
-    <hyperlink ref="B5" r:id="rId12" xr:uid="{852E5A38-45EB-4AD5-AE2D-22EF9086227F}"/>
-    <hyperlink ref="B6" r:id="rId13" xr:uid="{2A768213-2ED0-4D0B-A1B0-C1CAD783C141}"/>
-    <hyperlink ref="B7" r:id="rId14" xr:uid="{0DB1151B-B09D-4A38-91F2-EF044CC8FBCE}"/>
-    <hyperlink ref="B8" r:id="rId15" xr:uid="{9249A50C-40C8-4444-A0CE-9768526FA93D}"/>
-    <hyperlink ref="B9" r:id="rId16" xr:uid="{BEFAE6E9-8465-4E3C-87DA-75CA137290D2}"/>
-    <hyperlink ref="B10" r:id="rId17" xr:uid="{4D20A9AF-FD93-4072-B4A3-927FECB3A832}"/>
-    <hyperlink ref="B11" r:id="rId18" xr:uid="{3D2BEB49-EEE4-4196-861E-A9E5458BB091}"/>
-    <hyperlink ref="B12" r:id="rId19" xr:uid="{8E2B3C57-F7A9-4434-932B-0546FE34E890}"/>
-    <hyperlink ref="B13" r:id="rId20" xr:uid="{942F9D2D-CD35-4768-A578-C67E235FA74A}"/>
-    <hyperlink ref="B14" r:id="rId21" xr:uid="{4C836726-B4A2-49EC-810A-210030A4C2E3}"/>
-    <hyperlink ref="B15" r:id="rId22" xr:uid="{64561732-E3F8-4D9B-B4BC-BE202314B021}"/>
-    <hyperlink ref="B16" r:id="rId23" xr:uid="{2E2B4E1F-F20C-4771-A9FA-D770BC6C792A}"/>
-    <hyperlink ref="B17" r:id="rId24" xr:uid="{B4E6E8CC-C8EB-4ECC-8E15-E0F948C9BBA3}"/>
-    <hyperlink ref="B18" r:id="rId25" xr:uid="{30A55AF1-BFAB-4226-8452-6EC02665D7A7}"/>
-    <hyperlink ref="B19" r:id="rId26" xr:uid="{F17F0B7A-355C-42BE-A8A8-57229D500DFC}"/>
-    <hyperlink ref="B20" r:id="rId27" xr:uid="{02BAFC1F-A5EC-4C88-834D-EA254E8E7932}"/>
-    <hyperlink ref="B21" r:id="rId28" xr:uid="{46F1DACC-8279-4B65-B2E8-180FFD6A6099}"/>
-    <hyperlink ref="B22" r:id="rId29" xr:uid="{5A58FFEC-4163-4E9A-B9F0-63D7831237B9}"/>
-    <hyperlink ref="B23" r:id="rId30" xr:uid="{95537EFC-16D6-470E-A2A4-7223F8B77776}"/>
-    <hyperlink ref="B24" r:id="rId31" xr:uid="{4AFC6CD5-0CAE-4A18-A91F-072629FEE2A7}"/>
-    <hyperlink ref="B25" r:id="rId32" xr:uid="{1239B683-53FA-4E6C-8748-64E9DD71A754}"/>
-    <hyperlink ref="B26" r:id="rId33" xr:uid="{2F6E1D28-79CC-48FD-9520-188E0D4B9E6E}"/>
-    <hyperlink ref="B27" r:id="rId34" xr:uid="{1FE1900E-6AF8-4F52-BA70-B284B18ABBF1}"/>
-    <hyperlink ref="B28" r:id="rId35" xr:uid="{920FFFE5-9468-4AD7-953E-D6E1FD236CD0}"/>
-    <hyperlink ref="B29" r:id="rId36" xr:uid="{B87DAAA4-9E6E-44C4-9AFE-31018ED64428}"/>
-    <hyperlink ref="B30" r:id="rId37" xr:uid="{C9832A31-EDDE-4889-924D-436B55352EE6}"/>
-    <hyperlink ref="B31" r:id="rId38" xr:uid="{75C8795A-C2A3-492B-90D3-BF56A55E4997}"/>
-    <hyperlink ref="B32" r:id="rId39" xr:uid="{FC1696D1-EA78-4B1E-AC1F-60A18B78688C}"/>
-    <hyperlink ref="B33" r:id="rId40" xr:uid="{AB2E2D32-FFB1-4173-A121-E55F2D1CA349}"/>
-    <hyperlink ref="B34" r:id="rId41" xr:uid="{EA0DC3A3-AD62-48D3-BF2A-18FC1DA6A76A}"/>
-    <hyperlink ref="B35" r:id="rId42" xr:uid="{F801BE89-3ECD-48AE-9DB8-1C7E370ED74D}"/>
-    <hyperlink ref="B36" r:id="rId43" xr:uid="{CC30559D-78B7-4913-A852-BDE30DD40E2A}"/>
-    <hyperlink ref="B37" r:id="rId44" xr:uid="{90BED1DC-6EAC-4612-AF41-D394975532C8}"/>
-    <hyperlink ref="B38" r:id="rId45" xr:uid="{EADA49FE-8D29-4BA3-9877-FBBC51AED99F}"/>
-    <hyperlink ref="B39" r:id="rId46" xr:uid="{A06BC502-A2F2-4E26-BB67-1A1A6E9ED3E8}"/>
-    <hyperlink ref="B40" r:id="rId47" xr:uid="{46FB51B6-8731-4537-BE86-D0B3F6C1845F}"/>
-    <hyperlink ref="B41" r:id="rId48" xr:uid="{BEC72745-9257-4390-9D76-0A909665AE11}"/>
+    <hyperlink ref="B19" r:id="rId9" xr:uid="{DBFB8D0D-D925-4F2B-AC89-613C41E1ABC7}"/>
+    <hyperlink ref="B37" r:id="rId10" xr:uid="{F675ACE0-774F-468D-AAD9-5FC75B110487}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId49"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>